--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -39965,19 +39965,19 @@
         <v>46154</v>
       </c>
       <c r="B1599" t="n">
-        <v>4.454999923706055</v>
+        <v>4.463000297546387</v>
       </c>
       <c r="C1599" t="n">
-        <v>7353.9599609375</v>
+        <v>7400.9599609375</v>
       </c>
       <c r="D1599" t="n">
-        <v>18.94000053405762</v>
+        <v>17.98999977111816</v>
       </c>
       <c r="E1599" t="n">
-        <v>6763.483640136718</v>
+        <v>6763.718640136719</v>
       </c>
       <c r="F1599" t="n">
-        <v>4.351049971580506</v>
+        <v>4.351449990272522</v>
       </c>
       <c r="G1599" t="inlineStr">
         <is>
